--- a/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_1_weights.xlsx
+++ b/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_1_weights.xlsx
@@ -492,7 +492,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.007085370206312915</v>
+        <v>0.007085370206312917</v>
       </c>
       <c r="B2" t="n">
         <v>0.4667717100260344</v>
@@ -513,7 +513,7 @@
         <v>-0.729615911887192</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2460327161842266</v>
+        <v>0.2460327161842267</v>
       </c>
       <c r="I2" t="n">
         <v>0.3912314720815055</v>
@@ -534,7 +534,7 @@
         <v>-0.4784666190508798</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.06925915622198942</v>
+        <v>-0.06925915622198943</v>
       </c>
       <c r="P2" t="n">
         <v>-0.562090854717722</v>
@@ -566,7 +566,7 @@
         <v>-0.4690903376405988</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3312309949103183</v>
+        <v>-0.3312309949103184</v>
       </c>
       <c r="F3" t="n">
         <v>0.2726343844898807</v>
@@ -578,7 +578,7 @@
         <v>0.3305322953106442</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002139683641616822</v>
+        <v>0.002139683641616817</v>
       </c>
       <c r="J3" t="n">
         <v>-0.5302030448794499</v>
@@ -602,7 +602,7 @@
         <v>0.1443186992033145</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02472013585778908</v>
+        <v>0.02472013585778909</v>
       </c>
       <c r="R3" t="n">
         <v>-0.7907339660440885</v>
@@ -622,16 +622,16 @@
         <v>0.1471736109127853</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2579171003245915</v>
+        <v>-0.2579171003245914</v>
       </c>
       <c r="D4" t="n">
         <v>0.6566976661859543</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2351385733030103</v>
+        <v>-0.2351385733030104</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03450955288725733</v>
+        <v>0.03450955288725734</v>
       </c>
       <c r="G4" t="n">
         <v>0.1753435506067479</v>
@@ -673,7 +673,7 @@
         <v>-0.5781067248601984</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001499539133884917</v>
+        <v>0.001499539133884916</v>
       </c>
     </row>
     <row r="5">
@@ -714,7 +714,7 @@
         <v>-0.3066235392320191</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.50660148233017</v>
+        <v>-0.5066014823301699</v>
       </c>
       <c r="N5" t="n">
         <v>0.4866409437049583</v>
@@ -743,7 +743,7 @@
         <v>0.2511412169546842</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.04139790665590286</v>
+        <v>-0.04139790665590285</v>
       </c>
       <c r="C6" t="n">
         <v>-0.2201789558669512</v>
@@ -752,7 +752,7 @@
         <v>-0.3772362141753977</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.397422432164324</v>
+        <v>-0.3974224321643239</v>
       </c>
       <c r="F6" t="n">
         <v>-0.01239244739443347</v>
@@ -761,13 +761,13 @@
         <v>0.1862742349112841</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03634498726276969</v>
+        <v>0.03634498726276968</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0605379401026473</v>
+        <v>-0.06053794010264728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04755862311558506</v>
+        <v>0.04755862311558509</v>
       </c>
       <c r="K6" t="n">
         <v>-0.4631565859328619</v>
@@ -782,7 +782,7 @@
         <v>0.2556291486600803</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.03710170756204503</v>
+        <v>-0.03710170756204502</v>
       </c>
       <c r="P6" t="n">
         <v>0.1498873384104397</v>
@@ -841,7 +841,7 @@
         <v>0.2339567767837736</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3921984828358927</v>
+        <v>0.3921984828358926</v>
       </c>
       <c r="O7" t="n">
         <v>0.38499201272644</v>
@@ -853,13 +853,13 @@
         <v>0.2098168504726051</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.5302664015137173</v>
+        <v>-0.5302664015137174</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4006375064343417</v>
+        <v>0.4006375064343418</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06813208705523605</v>
+        <v>-0.06813208705523606</v>
       </c>
     </row>
   </sheetData>
